--- a/temp/demo.xlsx
+++ b/temp/demo.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\K盘\priviate\excelTransfer(2)\excelTransfer\temp\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="船厂" sheetId="13" r:id="rId1"/>
@@ -15,12 +20,12 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
+    <definedName name="______ASA87">'[1]FJ-1'!#REF!</definedName>
+    <definedName name="__ASA87" localSheetId="1">'[1]FJ-1'!#REF!</definedName>
     <definedName name="_ASA87" localSheetId="2">'[1]FJ-1'!#REF!</definedName>
-    <definedName name="__ASA87" localSheetId="1">'[1]FJ-1'!#REF!</definedName>
-    <definedName name="______ASA87">'[1]FJ-1'!#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">船厂!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">船东!$3:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">船检!$3:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">船东!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">船检!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +63,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t>AREA  (m</t>
     </r>
@@ -67,7 +72,7 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t>2</t>
     </r>
@@ -75,7 +80,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t>)</t>
     </r>
@@ -85,7 +90,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t xml:space="preserve">REMARK </t>
     </r>
@@ -93,7 +98,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t>(YARDREF.NO.)</t>
     </r>
@@ -106,6 +111,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>图</t>
@@ -114,7 +120,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t xml:space="preserve">        </t>
     </r>
@@ -122,6 +128,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>号</t>
@@ -132,6 +139,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>名</t>
@@ -140,7 +148,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t xml:space="preserve">         </t>
     </r>
@@ -148,6 +156,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>称</t>
@@ -158,6 +167,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>页</t>
@@ -166,7 +176,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -174,6 +184,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>数</t>
@@ -184,6 +195,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>面</t>
@@ -192,7 +204,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -200,6 +212,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>积</t>
@@ -210,6 +223,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>备</t>
@@ -218,7 +232,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <charset val="0"/>
+        <family val="1"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -226,6 +240,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>注</t>
@@ -235,17 +250,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0;\-#,##0;&quot;-&quot;"/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0;\-#,##0;&quot;-&quot;"/>
+    <numFmt numFmtId="178" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -259,12 +273,10 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -274,141 +286,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color indexed="36"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -421,29 +298,28 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <charset val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Geneva"/>
-      <charset val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="돋움"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -454,255 +330,55 @@
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="42"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="33">
+  <borders count="20">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -931,113 +607,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1049,190 +618,47 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="79">
+  <cellStyleXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1252,6 +678,90 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1260,203 +770,1365 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="79">
+  <cellStyles count="24">
+    <cellStyle name="Calc Currency (0)" xfId="1"/>
+    <cellStyle name="Header1" xfId="2"/>
+    <cellStyle name="Header2" xfId="3"/>
+    <cellStyle name="Normal_#18-Internet" xfId="4"/>
+    <cellStyle name="捠壿 [0.00]_laroux" xfId="5"/>
+    <cellStyle name="捠壿_laroux" xfId="6"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Calc Currency (0)" xfId="49"/>
-    <cellStyle name="Header1" xfId="50"/>
-    <cellStyle name="Header2" xfId="51"/>
-    <cellStyle name="Normal_#18-Internet" xfId="52"/>
-    <cellStyle name="捠壿 [0.00]_laroux" xfId="53"/>
-    <cellStyle name="捠壿_laroux" xfId="54"/>
-    <cellStyle name="常规 12 2 2 2" xfId="55"/>
-    <cellStyle name="常规 2" xfId="56"/>
-    <cellStyle name="常规 2 3" xfId="57"/>
-    <cellStyle name="常规 3" xfId="58"/>
-    <cellStyle name="常规 30" xfId="59"/>
-    <cellStyle name="常规 36" xfId="60"/>
-    <cellStyle name="常规 37" xfId="61"/>
-    <cellStyle name="常规 39" xfId="62"/>
-    <cellStyle name="常规 4" xfId="63"/>
-    <cellStyle name="常规 4 11" xfId="64"/>
-    <cellStyle name="常规 4 5" xfId="65"/>
-    <cellStyle name="常规 5" xfId="66"/>
-    <cellStyle name="常规 8" xfId="67"/>
-    <cellStyle name="常规_SC4282-401-01js" xfId="68"/>
-    <cellStyle name="常规_基本图纸目录 散货船 综合版" xfId="69"/>
-    <cellStyle name="常规_基本图纸目录 散货船 综合版 12" xfId="70"/>
-    <cellStyle name="常规_基本图纸目录 散货船 综合版 12 2" xfId="71"/>
-    <cellStyle name="常规_基本图纸目录 散货船 综合版 2 11" xfId="72"/>
-    <cellStyle name="常规_基本图纸目录 散货船 综合版 5" xfId="73"/>
-    <cellStyle name="常规_基本图纸目录 散货船 综合版 8" xfId="74"/>
-    <cellStyle name="货币 2" xfId="75"/>
-    <cellStyle name="昗弨_JP_NEW_9512" xfId="76"/>
-    <cellStyle name="寘嬫愗傝 [0.00]_laroux" xfId="77"/>
-    <cellStyle name="寘嬫愗傝_laroux" xfId="78"/>
+    <cellStyle name="常规 12 2 2 2" xfId="7"/>
+    <cellStyle name="常规 2" xfId="8"/>
+    <cellStyle name="常规 2 3" xfId="9"/>
+    <cellStyle name="常规 3" xfId="10"/>
+    <cellStyle name="常规 30" xfId="11"/>
+    <cellStyle name="常规 36" xfId="12"/>
+    <cellStyle name="常规 37" xfId="13"/>
+    <cellStyle name="常规 39" xfId="14"/>
+    <cellStyle name="常规 4" xfId="15"/>
+    <cellStyle name="常规 4 11" xfId="16"/>
+    <cellStyle name="常规 4 5" xfId="17"/>
+    <cellStyle name="常规 5" xfId="18"/>
+    <cellStyle name="常规 8" xfId="19"/>
+    <cellStyle name="货币 2" xfId="20"/>
+    <cellStyle name="昗弨_JP_NEW_9512" xfId="21"/>
+    <cellStyle name="寘嬫愗傝 [0.00]_laroux" xfId="22"/>
+    <cellStyle name="寘嬫愗傝_laroux" xfId="23"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="189">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1468,20 +2140,23 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00DA9694"/>
-      <color rgb="00000000"/>
+      <color rgb="FFDA9694"/>
+      <color rgb="FF000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1495,7 +2170,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="23135" name="Line 2"/>
         <xdr:cNvSpPr/>
@@ -1524,7 +2199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1538,7 +2213,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="25054" name="Line 2"/>
         <xdr:cNvSpPr/>
@@ -1576,7 +2251,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="Line 2"/>
         <xdr:cNvSpPr/>
@@ -1614,7 +2289,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="Line 2"/>
         <xdr:cNvSpPr/>
@@ -1643,7 +2318,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1657,7 +2332,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="24050" name="Line 2"/>
         <xdr:cNvSpPr/>
@@ -1695,7 +2370,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="Line 2"/>
         <xdr:cNvSpPr/>
@@ -1733,7 +2408,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="Line 2"/>
         <xdr:cNvSpPr/>
@@ -1762,7 +2437,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="xxxxxx"/>
@@ -2120,16 +2795,17 @@
       <a:lstStyle/>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="19.125" style="6" customWidth="1"/>
@@ -2140,425 +2816,424 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A1" s="38"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="43"/>
+    <row r="1" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="28"/>
     </row>
-    <row r="2" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="13"/>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="8"/>
     </row>
-    <row r="3" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23"/>
+    <row r="3" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="13"/>
     </row>
-    <row r="4" ht="32.25" customHeight="1" spans="1:6">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:6" ht="32.25" customHeight="1">
+      <c r="A4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:6">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="24" customHeight="1" spans="1:6">
-      <c r="A6" s="33"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="24" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="27"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="24" customHeight="1" spans="1:6">
-      <c r="A7" s="44"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="48"/>
+    <row r="7" spans="1:6" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="33"/>
     </row>
-    <row r="8" ht="15.15"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:E2"/>
   </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="JB6">
-    <cfRule type="expression" dxfId="0" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="188" priority="63" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SX6">
-    <cfRule type="expression" dxfId="0" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="62" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ACT6">
-    <cfRule type="expression" dxfId="0" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="61" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AMP6">
-    <cfRule type="expression" dxfId="0" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="60" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AWL6">
-    <cfRule type="expression" dxfId="0" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="59" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BGH6">
-    <cfRule type="expression" dxfId="0" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="58" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQD6">
-    <cfRule type="expression" dxfId="0" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="57" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BZZ6">
-    <cfRule type="expression" dxfId="0" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="56" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CJV6">
-    <cfRule type="expression" dxfId="0" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="55" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CTR6">
-    <cfRule type="expression" dxfId="0" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="54" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DDN6">
-    <cfRule type="expression" dxfId="0" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="53" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DNJ6">
-    <cfRule type="expression" dxfId="0" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="52" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DXF6">
-    <cfRule type="expression" dxfId="0" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="51" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EHB6">
-    <cfRule type="expression" dxfId="0" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="50" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQX6">
-    <cfRule type="expression" dxfId="0" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="49" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FAT6">
-    <cfRule type="expression" dxfId="0" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="48" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FKP6">
-    <cfRule type="expression" dxfId="0" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="47" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FUL6">
-    <cfRule type="expression" dxfId="0" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="46" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GEH6">
-    <cfRule type="expression" dxfId="0" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="45" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GOD6">
-    <cfRule type="expression" dxfId="0" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="44" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GXZ6">
-    <cfRule type="expression" dxfId="0" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="43" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HHV6">
-    <cfRule type="expression" dxfId="0" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="42" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HRR6">
-    <cfRule type="expression" dxfId="0" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="41" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IBN6">
-    <cfRule type="expression" dxfId="0" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="40" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ILJ6">
-    <cfRule type="expression" dxfId="0" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="39" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IVF6">
-    <cfRule type="expression" dxfId="0" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="38" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JFB6">
-    <cfRule type="expression" dxfId="0" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="37" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JOX6">
-    <cfRule type="expression" dxfId="0" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="36" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JYT6">
-    <cfRule type="expression" dxfId="0" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="35" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="KIP6">
-    <cfRule type="expression" dxfId="0" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="34" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="KSL6">
-    <cfRule type="expression" dxfId="0" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="33" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LCH6">
-    <cfRule type="expression" dxfId="0" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="32" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LMD6">
-    <cfRule type="expression" dxfId="0" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="31" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LVZ6">
-    <cfRule type="expression" dxfId="0" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="30" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MFV6">
-    <cfRule type="expression" dxfId="0" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="29" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MPR6">
-    <cfRule type="expression" dxfId="0" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="28" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MZN6">
-    <cfRule type="expression" dxfId="0" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="27" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="NJJ6">
-    <cfRule type="expression" dxfId="0" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="26" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="NTF6">
-    <cfRule type="expression" dxfId="0" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="25" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ODB6">
-    <cfRule type="expression" dxfId="0" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="24" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="OMX6">
-    <cfRule type="expression" dxfId="0" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="23" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="OWT6">
-    <cfRule type="expression" dxfId="0" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="22" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="PGP6">
-    <cfRule type="expression" dxfId="0" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="21" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="PQL6">
-    <cfRule type="expression" dxfId="0" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="20" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QAH6">
-    <cfRule type="expression" dxfId="0" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="19" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QKD6">
-    <cfRule type="expression" dxfId="0" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="18" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QTZ6">
-    <cfRule type="expression" dxfId="0" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="17" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RDV6">
-    <cfRule type="expression" dxfId="0" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="16" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RNR6">
-    <cfRule type="expression" dxfId="0" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="15" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RXN6">
-    <cfRule type="expression" dxfId="0" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="14" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SHJ6">
-    <cfRule type="expression" dxfId="0" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="13" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SRF6">
-    <cfRule type="expression" dxfId="0" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="12" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TBB6">
-    <cfRule type="expression" dxfId="0" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="11" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TKX6">
-    <cfRule type="expression" dxfId="0" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="10" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TUT6">
-    <cfRule type="expression" dxfId="0" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="9" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UEP6">
-    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="8" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UOL6">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="7" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UYH6">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="6" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="VID6">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="5" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="VRZ6">
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="4" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="WBV6">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="3" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="WLR6">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="2" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="WVN6">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>"$W-$X"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.66875" right="0.156944444444444" top="0.393055555555556" bottom="0.196527777777778" header="0.156944444444444" footer="0.236111111111111"/>
-  <pageSetup paperSize="9" scale="85" firstPageNumber="2" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="600" verticalDpi="600"/>
+    <cfRule type="expression" dxfId="126" priority="1" stopIfTrue="1">
+      <formula>"$W-$X"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.6692913385826772" right="0.15748031496062992" top="0.39370078740157483" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.23622047244094491"/>
+  <pageSetup paperSize="9" scale="85" firstPageNumber="2" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;R
-&amp;P/&amp;N+1
-      </oddHeader>
+&amp;P</oddHeader>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="19.125" style="6" customWidth="1"/>
@@ -2569,423 +3244,425 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="13"/>
+    <row r="1" spans="1:6" ht="26.25" customHeight="1" thickTop="1">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="28"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="13"/>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="8"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23"/>
+    <row r="3" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="13"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="32.25" customHeight="1" spans="1:6">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:6" ht="32.25" customHeight="1">
+      <c r="A4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:6">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="24" customHeight="1" spans="1:6">
-      <c r="A6" s="33"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="24" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="27"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="24" customHeight="1" spans="1:6">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
+    <row r="7" spans="1:6" s="4" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="33"/>
     </row>
+    <row r="8" spans="1:6" ht="14.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:E2"/>
   </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="JB6">
-    <cfRule type="expression" dxfId="0" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="63" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SX6">
-    <cfRule type="expression" dxfId="0" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="62" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ACT6">
-    <cfRule type="expression" dxfId="0" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="61" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AMP6">
-    <cfRule type="expression" dxfId="0" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="60" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AWL6">
-    <cfRule type="expression" dxfId="0" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="59" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BGH6">
-    <cfRule type="expression" dxfId="0" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="58" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQD6">
-    <cfRule type="expression" dxfId="0" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="57" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BZZ6">
-    <cfRule type="expression" dxfId="0" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="56" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CJV6">
-    <cfRule type="expression" dxfId="0" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="55" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CTR6">
-    <cfRule type="expression" dxfId="0" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="54" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DDN6">
-    <cfRule type="expression" dxfId="0" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="53" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DNJ6">
-    <cfRule type="expression" dxfId="0" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="52" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DXF6">
-    <cfRule type="expression" dxfId="0" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="51" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EHB6">
-    <cfRule type="expression" dxfId="0" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="50" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQX6">
-    <cfRule type="expression" dxfId="0" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="49" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FAT6">
-    <cfRule type="expression" dxfId="0" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="48" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FKP6">
-    <cfRule type="expression" dxfId="0" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="47" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FUL6">
-    <cfRule type="expression" dxfId="0" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="46" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GEH6">
-    <cfRule type="expression" dxfId="0" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="45" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GOD6">
-    <cfRule type="expression" dxfId="0" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="44" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GXZ6">
-    <cfRule type="expression" dxfId="0" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="43" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HHV6">
-    <cfRule type="expression" dxfId="0" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="42" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HRR6">
-    <cfRule type="expression" dxfId="0" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="41" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IBN6">
-    <cfRule type="expression" dxfId="0" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="40" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ILJ6">
-    <cfRule type="expression" dxfId="0" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="39" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IVF6">
-    <cfRule type="expression" dxfId="0" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="38" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JFB6">
-    <cfRule type="expression" dxfId="0" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="37" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JOX6">
-    <cfRule type="expression" dxfId="0" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="36" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JYT6">
-    <cfRule type="expression" dxfId="0" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="35" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="KIP6">
-    <cfRule type="expression" dxfId="0" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="34" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="KSL6">
-    <cfRule type="expression" dxfId="0" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="33" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LCH6">
-    <cfRule type="expression" dxfId="0" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="32" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LMD6">
-    <cfRule type="expression" dxfId="0" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="31" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LVZ6">
-    <cfRule type="expression" dxfId="0" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="30" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MFV6">
-    <cfRule type="expression" dxfId="0" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="29" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MPR6">
-    <cfRule type="expression" dxfId="0" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="28" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MZN6">
-    <cfRule type="expression" dxfId="0" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="27" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="NJJ6">
-    <cfRule type="expression" dxfId="0" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="26" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="NTF6">
-    <cfRule type="expression" dxfId="0" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="25" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ODB6">
-    <cfRule type="expression" dxfId="0" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="24" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="OMX6">
-    <cfRule type="expression" dxfId="0" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="23" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="OWT6">
-    <cfRule type="expression" dxfId="0" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="22" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="PGP6">
-    <cfRule type="expression" dxfId="0" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="21" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="PQL6">
-    <cfRule type="expression" dxfId="0" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="20" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QAH6">
-    <cfRule type="expression" dxfId="0" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="19" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QKD6">
-    <cfRule type="expression" dxfId="0" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="18" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QTZ6">
-    <cfRule type="expression" dxfId="0" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="17" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RDV6">
-    <cfRule type="expression" dxfId="0" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="16" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RNR6">
-    <cfRule type="expression" dxfId="0" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="15" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RXN6">
-    <cfRule type="expression" dxfId="0" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="14" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SHJ6">
-    <cfRule type="expression" dxfId="0" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="13" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SRF6">
-    <cfRule type="expression" dxfId="0" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="12" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TBB6">
-    <cfRule type="expression" dxfId="0" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="11" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TKX6">
-    <cfRule type="expression" dxfId="0" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="10" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TUT6">
-    <cfRule type="expression" dxfId="0" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="9" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UEP6">
-    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="8" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UOL6">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="7" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UYH6">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="6" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="VID6">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="5" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="VRZ6">
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="4" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="WBV6">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="3" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="WLR6">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="2" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="WVN6">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>"$W-$X"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.669291338582677" right="0.15748031496063" top="0.393700787401575" bottom="0.196850393700787" header="0.15748031496063" footer="0.236220472440945"/>
-  <pageSetup paperSize="9" scale="85" firstPageNumber="2" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="600" verticalDpi="600"/>
+    <cfRule type="expression" dxfId="63" priority="1" stopIfTrue="1">
+      <formula>"$W-$X"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.6692913385826772" right="0.15748031496062992" top="0.39370078740157483" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.23622047244094491"/>
+  <pageSetup paperSize="9" scale="85" firstPageNumber="2" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;R&amp;"Times New Roman,常规"
-&amp;P/&amp;N+1      </oddHeader>
+&amp;P</oddHeader>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="19.125" style="6" customWidth="1"/>
@@ -2996,398 +3673,400 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="13"/>
+    <row r="1" spans="1:6" ht="26.25" customHeight="1" thickTop="1">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="28"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="13"/>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="8"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="26.25" customHeight="1" spans="1:6">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23"/>
+    <row r="3" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="13"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="32.25" customHeight="1" spans="1:6">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:6" ht="32.25" customHeight="1">
+      <c r="A4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:6">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="24" customHeight="1" spans="1:6">
-      <c r="A6" s="33"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="24" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="27"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="24" customHeight="1" spans="1:6">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
+    <row r="7" spans="1:6" s="4" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="33"/>
     </row>
+    <row r="8" spans="1:6" ht="14.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:E2"/>
   </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="JB6">
-    <cfRule type="expression" dxfId="0" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="63" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SX6">
-    <cfRule type="expression" dxfId="0" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="62" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ACT6">
-    <cfRule type="expression" dxfId="0" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="61" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AMP6">
-    <cfRule type="expression" dxfId="0" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="60" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AWL6">
-    <cfRule type="expression" dxfId="0" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BGH6">
-    <cfRule type="expression" dxfId="0" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQD6">
-    <cfRule type="expression" dxfId="0" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BZZ6">
-    <cfRule type="expression" dxfId="0" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CJV6">
-    <cfRule type="expression" dxfId="0" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CTR6">
-    <cfRule type="expression" dxfId="0" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DDN6">
-    <cfRule type="expression" dxfId="0" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DNJ6">
-    <cfRule type="expression" dxfId="0" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DXF6">
-    <cfRule type="expression" dxfId="0" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EHB6">
-    <cfRule type="expression" dxfId="0" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EQX6">
-    <cfRule type="expression" dxfId="0" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FAT6">
-    <cfRule type="expression" dxfId="0" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FKP6">
-    <cfRule type="expression" dxfId="0" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FUL6">
-    <cfRule type="expression" dxfId="0" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GEH6">
-    <cfRule type="expression" dxfId="0" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GOD6">
-    <cfRule type="expression" dxfId="0" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GXZ6">
-    <cfRule type="expression" dxfId="0" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HHV6">
-    <cfRule type="expression" dxfId="0" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HRR6">
-    <cfRule type="expression" dxfId="0" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IBN6">
-    <cfRule type="expression" dxfId="0" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="40" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ILJ6">
-    <cfRule type="expression" dxfId="0" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="39" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IVF6">
-    <cfRule type="expression" dxfId="0" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JFB6">
-    <cfRule type="expression" dxfId="0" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JOX6">
-    <cfRule type="expression" dxfId="0" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JYT6">
-    <cfRule type="expression" dxfId="0" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="KIP6">
-    <cfRule type="expression" dxfId="0" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="KSL6">
-    <cfRule type="expression" dxfId="0" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LCH6">
-    <cfRule type="expression" dxfId="0" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LMD6">
-    <cfRule type="expression" dxfId="0" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="31" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="LVZ6">
-    <cfRule type="expression" dxfId="0" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="30" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MFV6">
-    <cfRule type="expression" dxfId="0" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MPR6">
-    <cfRule type="expression" dxfId="0" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="28" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="MZN6">
-    <cfRule type="expression" dxfId="0" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="27" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="NJJ6">
-    <cfRule type="expression" dxfId="0" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="26" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="NTF6">
-    <cfRule type="expression" dxfId="0" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="25" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ODB6">
-    <cfRule type="expression" dxfId="0" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="24" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="OMX6">
-    <cfRule type="expression" dxfId="0" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="23" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="OWT6">
-    <cfRule type="expression" dxfId="0" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="22" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="PGP6">
-    <cfRule type="expression" dxfId="0" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="21" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="PQL6">
-    <cfRule type="expression" dxfId="0" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="20" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QAH6">
-    <cfRule type="expression" dxfId="0" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="19" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QKD6">
-    <cfRule type="expression" dxfId="0" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="18" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="QTZ6">
-    <cfRule type="expression" dxfId="0" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="17" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RDV6">
-    <cfRule type="expression" dxfId="0" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="16" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RNR6">
-    <cfRule type="expression" dxfId="0" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="15" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="RXN6">
-    <cfRule type="expression" dxfId="0" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="14" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SHJ6">
-    <cfRule type="expression" dxfId="0" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="13" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="SRF6">
-    <cfRule type="expression" dxfId="0" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="12" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TBB6">
-    <cfRule type="expression" dxfId="0" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="11" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TKX6">
-    <cfRule type="expression" dxfId="0" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="10" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="TUT6">
-    <cfRule type="expression" dxfId="0" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="9" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UEP6">
-    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UOL6">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="UYH6">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="VID6">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="VRZ6">
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="WBV6">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="WLR6">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3396,12 +4075,12 @@
       <formula>"$W-$X"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.669291338582677" right="0.15748031496063" top="0.393700787401575" bottom="0.393700787401575" header="0.15748031496063" footer="0.236220472440945"/>
-  <pageSetup paperSize="9" scale="85" firstPageNumber="2" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="600" verticalDpi="600"/>
+  <pageMargins left="0.6692913385826772" right="0.15748031496062992" top="0.39370078740157483" bottom="0.39370078740157483" header="0.15748031496062992" footer="0.23622047244094491"/>
+  <pageSetup paperSize="9" scale="85" firstPageNumber="2" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;R&amp;"Times New Roman,常规"
-&amp;P/&amp;N+1      </oddHeader>
+&amp;P</oddHeader>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>